--- a/output/roomself_excel/3732.xlsx
+++ b/output/roomself_excel/3732.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>85932</v>
+        <v>52799</v>
       </c>
       <c r="D2" t="n">
-        <v>2372</v>
+        <v>1876</v>
       </c>
       <c r="E2" t="n">
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -492,16 +492,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>331777</v>
+        <v>207130</v>
       </c>
       <c r="D3" t="n">
-        <v>7140</v>
+        <v>4140</v>
       </c>
       <c r="E3" t="n">
-        <v>884</v>
+        <v>590</v>
       </c>
       <c r="F3" t="n">
-        <v>818</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44525</v>
+        <v>85932</v>
       </c>
       <c r="D4" t="n">
-        <v>1848</v>
+        <v>2372</v>
       </c>
       <c r="E4" t="n">
-        <v>183</v>
+        <v>380</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>23023</v>
+        <v>44525</v>
       </c>
       <c r="D6" t="n">
-        <v>1216</v>
+        <v>1848</v>
       </c>
       <c r="E6" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21593</v>
+        <v>71848</v>
       </c>
       <c r="D7" t="n">
-        <v>1176</v>
+        <v>2648</v>
       </c>
       <c r="E7" t="n">
-        <v>151</v>
+        <v>423</v>
       </c>
       <c r="F7" t="n">
-        <v>27</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8">
@@ -598,19 +598,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>21593</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1176</v>
+      </c>
+      <c r="E8" t="n">
+        <v>151</v>
+      </c>
+      <c r="F8" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C8" t="n">
+      <c r="C9" t="n">
+        <v>23023</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1216</v>
+      </c>
+      <c r="E9" t="n">
+        <v>161</v>
+      </c>
+      <c r="F9" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>10530</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D10" t="n">
         <v>852</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E10" t="n">
         <v>162</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F10" t="n">
         <v>105</v>
       </c>
     </row>

--- a/output/roomself_excel/3732.xlsx
+++ b/output/roomself_excel/3732.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,32 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
         </is>
       </c>
     </row>
@@ -475,12 +495,20 @@
       <c r="D2" t="n">
         <v>1876</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
-      </c>
+        <v>243</v>
+      </c>
+      <c r="G2" t="n">
+        <v>33</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,11 +525,27 @@
       <c r="D3" t="n">
         <v>4140</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>590</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>39</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>201</v>
+      </c>
+      <c r="J3" t="n">
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -519,11 +563,27 @@
       <c r="D4" t="n">
         <v>2372</v>
       </c>
-      <c r="E4" t="n">
-        <v>380</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>279</v>
+        <v>252</v>
+      </c>
+      <c r="G4" t="n">
+        <v>39</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>341</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +601,26 @@
       <c r="D5" t="n">
         <v>2376</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>293</v>
+      </c>
+      <c r="G5" t="n">
+        <v>33</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>301</v>
       </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
         <v>27</v>
       </c>
     </row>
@@ -563,12 +639,12 @@
       <c r="D6" t="n">
         <v>1848</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,11 +661,27 @@
       <c r="D7" t="n">
         <v>2648</v>
       </c>
-      <c r="E7" t="n">
-        <v>423</v>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F7" t="n">
-        <v>228</v>
+        <v>248</v>
+      </c>
+      <c r="G7" t="n">
+        <v>27</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>110</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -607,12 +699,20 @@
       <c r="D8" t="n">
         <v>1176</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>151</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>27</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +729,20 @@
       <c r="D9" t="n">
         <v>1216</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>161</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>27</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,11 +759,27 @@
       <c r="D10" t="n">
         <v>852</v>
       </c>
-      <c r="E10" t="n">
-        <v>162</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>105</v>
+        <v>135</v>
+      </c>
+      <c r="G10" t="n">
+        <v>27</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>78</v>
+      </c>
+      <c r="J10" t="n">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
